--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9255586859</v>
+        <v>46157.93114046878</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114046878</v>
+        <v>46157.9313731047</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313731047</v>
+        <v>46157.93384855406</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384855406</v>
+        <v>46157.93696479388</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696479388</v>
+        <v>46158.28205357662</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205357662</v>
+        <v>46158.29653305702</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653305702</v>
+        <v>46158.29808516306</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808516306</v>
+        <v>46158.33371178014</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371178014</v>
+        <v>46158.37222542494</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Февраль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222542494</v>
+        <v>46158.37276033647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
